--- a/celebrities.xlsx
+++ b/celebrities.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\33543\Desktop\ML\Group\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78DF7CE2-92D2-43C0-BA07-4503C4F6154A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3783D631-BD64-4E62-A325-2605A59705E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="82">
   <si>
     <t>Name</t>
   </si>
@@ -259,6 +259,18 @@
   </si>
   <si>
     <t>Tailored; Edgy; Minimalist</t>
+  </si>
+  <si>
+    <t>Sdanny Lee</t>
+  </si>
+  <si>
+    <t>Singer /Performer</t>
+  </si>
+  <si>
+    <t>Known for bold stage presence and modern fashion-forward styling.</t>
+  </si>
+  <si>
+    <t>Modern, Stage, Bold</t>
   </si>
 </sst>
 </file>
@@ -302,7 +314,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -312,6 +324,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -593,7 +608,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="5" width="36.6328125" style="3" customWidth="1"/>
@@ -956,6 +971,30 @@
         <v>77</v>
       </c>
     </row>
+    <row r="22" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A22" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22" t="s">
+        <v>79</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B24"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/celebrities.xlsx
+++ b/celebrities.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\33543\Desktop\ML\Group\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3783D631-BD64-4E62-A325-2605A59705E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13D9268E-34C3-4A41-8846-9A7E8B7BAD91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="84">
   <si>
     <t>Name</t>
   </si>
@@ -271,6 +271,12 @@
   </si>
   <si>
     <t>Modern, Stage, Bold</t>
+  </si>
+  <si>
+    <t>ImageURL</t>
+  </si>
+  <si>
+    <t>https://huggingface.co/datasets/sherry2026/celebrity/resolve/main/artist1.jpg</t>
   </si>
 </sst>
 </file>
@@ -608,13 +614,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="5" width="36.6328125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -630,8 +637,11 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="F1" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -648,7 +658,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -665,7 +675,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>15</v>
       </c>
@@ -682,7 +692,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>20</v>
       </c>
@@ -699,7 +709,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>24</v>
       </c>
@@ -716,7 +726,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>27</v>
       </c>
@@ -733,7 +743,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>30</v>
       </c>
@@ -750,7 +760,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>33</v>
       </c>
@@ -767,7 +777,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>37</v>
       </c>
@@ -784,7 +794,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>41</v>
       </c>
@@ -801,7 +811,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>44</v>
       </c>
@@ -818,7 +828,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>48</v>
       </c>
@@ -835,7 +845,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>52</v>
       </c>
@@ -852,7 +862,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>55</v>
       </c>
@@ -869,7 +879,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>58</v>
       </c>
@@ -886,7 +896,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>61</v>
       </c>
@@ -903,7 +913,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>64</v>
       </c>
@@ -920,7 +930,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>67</v>
       </c>
@@ -937,7 +947,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>71</v>
       </c>
@@ -954,7 +964,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>75</v>
       </c>
@@ -971,7 +981,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
         <v>78</v>
       </c>
@@ -987,12 +997,15 @@
       <c r="E22" s="4" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F22" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B24"/>
     </row>
   </sheetData>

--- a/celebrities.xlsx
+++ b/celebrities.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\33543\Desktop\ML\Group\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{393FC0F0-CD35-4150-B225-969342433A1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0DE6F16-18A8-476E-9B5F-0BB198228E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -114,13 +114,13 @@
     <t>https://huggingface.co/datasets/sherry2026/celebrity/resolve/main/rose.jpg</t>
   </si>
   <si>
-    <t>https://huggingface.co/datasets/sherry2026/celebrity/resolve/main/TaylorSwift.jpg</t>
-  </si>
-  <si>
-    <t>https://huggingface.co/datasets/sherry2026/celebrity/resolve/main/BillieEilish.jpg</t>
-  </si>
-  <si>
-    <t>https://huggingface.co/datasets/sherry2026/celebrity/resolve/main/SdannyLee.jpg</t>
+    <t>https://huggingface.co/datasets/sherry2026/celebrity/resolve/main/Taylor%20Swift.jpg</t>
+  </si>
+  <si>
+    <t>https://huggingface.co/datasets/sherry2026/celebrity/resolve/main/Billie%20Eilish.jpg</t>
+  </si>
+  <si>
+    <t>https://huggingface.co/datasets/sherry2026/celebrity/resolve/main/Sdanny%20Lee.jpg</t>
   </si>
 </sst>
 </file>
@@ -552,7 +552,7 @@
       <c r="E4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" t="s">
         <v>30</v>
       </c>
     </row>
@@ -572,7 +572,7 @@
       <c r="E5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="5" t="s">
         <v>28</v>
       </c>
     </row>
@@ -605,10 +605,10 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" xr:uid="{4F30DF5E-FCA0-4B6C-8C6E-D465C6FC93A1}"/>
-    <hyperlink ref="F3" r:id="rId2" xr:uid="{BA4071B9-274F-41AD-AFF1-44CD5A557BA3}"/>
-    <hyperlink ref="F4" r:id="rId3" xr:uid="{E9E22502-3C60-447E-BF62-2947E1C64DB5}"/>
-    <hyperlink ref="F6" r:id="rId4" xr:uid="{9B0E928E-67B9-48E0-8B39-A0666DE1998C}"/>
+    <hyperlink ref="F2" r:id="rId1" xr:uid="{C5E4B323-82E8-433E-8C37-7E8146DF06CB}"/>
+    <hyperlink ref="F3" r:id="rId2" xr:uid="{EB3DE857-2039-411B-A4B6-75B7743BABF3}"/>
+    <hyperlink ref="F5" r:id="rId3" xr:uid="{E31A396B-6EFA-4CE3-B377-68C761E11A38}"/>
+    <hyperlink ref="F6" r:id="rId4" xr:uid="{96D82356-5F7E-4937-BCC2-8F7496642879}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
